--- a/basedatos_partidas/salida/descompuestos/CT-12-06-010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-12-06-010.xlsx
@@ -539,10 +539,10 @@
         <v>2.1</v>
       </c>
       <c r="G10" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="H10" t="n">
-        <v>9.66</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="11">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>17.93</v>
+        <v>14.15</v>
       </c>
     </row>
     <row r="15">
@@ -730,10 +730,10 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>25.77</v>
+        <v>21.99</v>
       </c>
       <c r="H20" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="21">
@@ -749,7 +749,7 @@
       </c>
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="5" t="n">
-        <v>26.03</v>
+        <v>22.21</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-12-06-010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-12-06-010.xlsx
@@ -617,10 +617,10 @@
         <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="H13" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>14.15</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="15">
@@ -730,10 +730,10 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>21.99</v>
+        <v>22.74</v>
       </c>
       <c r="H20" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="21">
@@ -749,7 +749,7 @@
       </c>
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="5" t="n">
-        <v>22.21</v>
+        <v>22.97</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-12-06-010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-12-06-010.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 12 Instalaciones sanitarias</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Puntos de desagüe</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
